--- a/templates/WITNESSING_WIRE_TEMPLATE.xlsx
+++ b/templates/WITNESSING_WIRE_TEMPLATE.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>RECEIVED KICO SEAL</t>
+          <t>RECEIVED MINE SEAL</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RECEIVED KICO SEAL  &lt;-  RECEIVED KICO SEAL</t>
+          <t>RECEIVED MINE SEAL  &lt;-  RECEIVED MINE SEAL</t>
         </is>
       </c>
     </row>
